--- a/data/trans_orig/LAWTONB_2R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35688</t>
+          <t>34940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61147</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56372</t>
+          <t>54939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84396</t>
+          <t>82940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99229</t>
+          <t>96738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138330</t>
+          <t>135354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231436</t>
+          <t>232148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>256895</t>
+          <t>257643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258538</t>
+          <t>259994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286562</t>
+          <t>287995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497187</t>
+          <t>500163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>536288</t>
+          <t>538779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71324</t>
+          <t>71107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97967</t>
+          <t>99801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144380</t>
+          <t>145379</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182358</t>
+          <t>181177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>223269</t>
+          <t>225913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>272473</t>
+          <t>273767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111916</t>
+          <t>110082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>138559</t>
+          <t>138776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151550</t>
+          <t>152731</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>189528</t>
+          <t>188529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>271318</t>
+          <t>270024</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320522</t>
+          <t>317878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115143</t>
+          <t>114256</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152959</t>
+          <t>153418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209951</t>
+          <t>209277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260274</t>
+          <t>259970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>332744</t>
+          <t>334693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>395723</t>
+          <t>394645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>349048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>387323</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416568</t>
+          <t>416872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>466891</t>
+          <t>467565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>784663</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>846564</t>
+          <t>844615</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35075</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>62722</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61056</t>
+          <t>59679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92518</t>
+          <t>92095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101596</t>
+          <t>102097</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141557</t>
+          <t>145729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249569</t>
+          <t>247064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274711</t>
+          <t>274316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261478</t>
+          <t>261901</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292940</t>
+          <t>294317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522225</t>
+          <t>518053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562186</t>
+          <t>561685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86616</t>
+          <t>86863</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121406</t>
+          <t>120256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>191201</t>
+          <t>191095</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>232712</t>
+          <t>232493</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>289609</t>
+          <t>290260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>342695</t>
+          <t>343448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128445</t>
+          <t>129595</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163235</t>
+          <t>162988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>156267</t>
+          <t>156486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>197778</t>
+          <t>197884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296135</t>
+          <t>295382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>349221</t>
+          <t>348570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127667</t>
+          <t>127896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172407</t>
+          <t>172620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>260717</t>
+          <t>258686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>316377</t>
+          <t>313752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>400732</t>
+          <t>400904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>470735</t>
+          <t>469767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387230</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>431970</t>
+          <t>431741</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>426598</t>
+          <t>429223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>482258</t>
+          <t>484289</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>831877</t>
+          <t>832845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>901880</t>
+          <t>901708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45192</t>
+          <t>45721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70124</t>
+          <t>68427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105384</t>
+          <t>99779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98775</t>
+          <t>97939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136254</t>
+          <t>138607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289138</t>
+          <t>288609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310882</t>
+          <t>310626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272378</t>
+          <t>277983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307638</t>
+          <t>309335</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575838</t>
+          <t>573485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>613317</t>
+          <t>614153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77892</t>
+          <t>76726</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>105579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>171126</t>
+          <t>170311</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217406</t>
+          <t>214353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258176</t>
+          <t>258181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312804</t>
+          <t>310305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>152609</t>
+          <t>151419</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179106</t>
+          <t>180272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182763</t>
+          <t>185816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>229043</t>
+          <t>229858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344363</t>
+          <t>346862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398991</t>
+          <t>398986</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105641</t>
+          <t>105867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143942</t>
+          <t>143017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>251097</t>
+          <t>248112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>306449</t>
+          <t>305455</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>367801</t>
+          <t>364334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>438824</t>
+          <t>433164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>447386</t>
+          <t>448311</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>485687</t>
+          <t>485461</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>471482</t>
+          <t>472476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>526834</t>
+          <t>529819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>930435</t>
+          <t>936095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1001458</t>
+          <t>1004925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>56090</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41994</t>
+          <t>44826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61995</t>
+          <t>68615</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>81089</t>
+          <t>89497</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34933</t>
+          <t>77196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128071</t>
+          <t>102212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>132572</t>
+          <t>145587</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71046</t>
+          <t>128831</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174991</t>
+          <t>161717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -4618,32 +4618,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>312973</t>
+          <t>347050</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302461</t>
+          <t>334525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>322462</t>
+          <t>358314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>525499</t>
+          <t>347823</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>478517</t>
+          <t>335108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571655</t>
+          <t>360124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4688,32 +4688,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>838473</t>
+          <t>694873</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>796054</t>
+          <t>678743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>899999</t>
+          <t>711629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -4731,17 +4731,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>364456</t>
+          <t>403140</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>364456</t>
+          <t>403140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>364456</t>
+          <t>403140</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>437320</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>437320</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>437320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>971045</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>971045</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>971045</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>119367</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99524</t>
+          <t>105856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125678</t>
+          <t>133594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>259798</t>
+          <t>281265</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>246106</t>
+          <t>265119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272400</t>
+          <t>295444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>371320</t>
+          <t>400631</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>351491</t>
+          <t>379031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390440</t>
+          <t>421575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -4961,32 +4961,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>168426</t>
+          <t>187700</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154270</t>
+          <t>173473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180424</t>
+          <t>201211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>162837</t>
+          <t>179633</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150235</t>
+          <t>165454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176529</t>
+          <t>195779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5031,32 +5031,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>331263</t>
+          <t>367333</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>312143</t>
+          <t>346389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>351092</t>
+          <t>388933</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -5074,17 +5074,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>422635</t>
+          <t>460898</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>422635</t>
+          <t>460898</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>422635</t>
+          <t>460898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>702583</t>
+          <t>767964</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>702583</t>
+          <t>767964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>702583</t>
+          <t>767964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>163005</t>
+          <t>175457</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145589</t>
+          <t>158954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180902</t>
+          <t>197033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>340887</t>
+          <t>370762</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179236</t>
+          <t>348962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>433745</t>
+          <t>390260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>503892</t>
+          <t>546218</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344724</t>
+          <t>517575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>586783</t>
+          <t>577032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -5304,32 +5304,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>481399</t>
+          <t>534750</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463502</t>
+          <t>513174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>498815</t>
+          <t>551253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>688337</t>
+          <t>527456</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>595479</t>
+          <t>507958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>849988</t>
+          <t>549256</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5374,32 +5374,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1169736</t>
+          <t>1062206</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1086845</t>
+          <t>1031392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328904</t>
+          <t>1090849</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -5417,17 +5417,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
